--- a/北総FAS状況/プランナー一覧.xlsx
+++ b/北総FAS状況/プランナー一覧.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="82">
   <si>
     <t>CD</t>
   </si>
@@ -282,7 +282,6 @@
     <font>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -318,13 +317,13 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1182,39 +1181,31 @@
       </c>
     </row>
     <row r="36" ht="18.75" customHeight="1">
-      <c r="A36" s="2">
-        <v>1301.0</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>48</v>
-      </c>
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="1">
-        <v>1.0</v>
-      </c>
+      <c r="D36" s="2"/>
       <c r="E36" s="2"/>
-      <c r="F36" s="2">
-        <v>101478.0</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="2">
-        <v>1511.0</v>
+        <v>1301.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C37" s="4"/>
-      <c r="D37" s="2"/>
+      <c r="D37" s="1">
+        <v>1.0</v>
+      </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2">
-        <v>116579.0</v>
+        <v>101478.0</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" ht="18.75" customHeight="1">
@@ -1228,10 +1219,10 @@
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2">
-        <v>101221.0</v>
+        <v>116579.0</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" ht="18.75" customHeight="1">
@@ -1245,10 +1236,10 @@
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2">
-        <v>101815.0</v>
+        <v>101221.0</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" ht="18.75" customHeight="1">
@@ -1259,15 +1250,13 @@
         <v>50</v>
       </c>
       <c r="C40" s="4"/>
-      <c r="D40" s="1">
-        <v>1.0</v>
-      </c>
+      <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2">
-        <v>132011.0</v>
+        <v>101815.0</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" ht="18.75" customHeight="1">
@@ -1277,18 +1266,16 @@
       <c r="B41" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>55</v>
-      </c>
+      <c r="C41" s="4"/>
       <c r="D41" s="1">
         <v>1.0</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2">
-        <v>130877.0</v>
+        <v>132011.0</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" ht="18.75" customHeight="1">
@@ -1298,16 +1285,18 @@
       <c r="B42" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C42" s="4"/>
+      <c r="C42" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="D42" s="1">
         <v>1.0</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2">
-        <v>131810.0</v>
+        <v>130877.0</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43" ht="18.75" customHeight="1">
@@ -1318,13 +1307,15 @@
         <v>50</v>
       </c>
       <c r="C43" s="4"/>
-      <c r="D43" s="2"/>
+      <c r="D43" s="1">
+        <v>1.0</v>
+      </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2">
-        <v>115159.0</v>
+        <v>131810.0</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44" ht="18.75" customHeight="1">
@@ -1338,27 +1329,27 @@
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2">
-        <v>116561.0</v>
+        <v>115159.0</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" s="2">
-        <v>1554.0</v>
+        <v>1511.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C45" s="4"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2">
-        <v>116413.0</v>
+        <v>116561.0</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" ht="18.75" customHeight="1">
@@ -1372,10 +1363,10 @@
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2">
-        <v>131831.0</v>
+        <v>116413.0</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" ht="18.75" customHeight="1">
@@ -1389,10 +1380,10 @@
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2">
-        <v>101252.0</v>
+        <v>131831.0</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="48" ht="18.75" customHeight="1">
@@ -1406,10 +1397,10 @@
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2">
-        <v>133403.0</v>
+        <v>101252.0</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49" ht="18.75" customHeight="1">
@@ -1423,31 +1414,27 @@
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2">
-        <v>116661.0</v>
+        <v>133403.0</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="50" ht="18.75" customHeight="1">
       <c r="A50" s="2">
-        <v>1556.0</v>
+        <v>1554.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D50" s="1">
-        <v>1.0</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="C50" s="4"/>
+      <c r="D50" s="2"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2">
-        <v>116685.0</v>
+        <v>116661.0</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="51" ht="18.75" customHeight="1">
@@ -1458,17 +1445,17 @@
         <v>66</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="D51" s="1">
         <v>1.0</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2">
-        <v>101328.0</v>
+        <v>116685.0</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52" ht="18.75" customHeight="1">
@@ -1486,10 +1473,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2">
-        <v>130581.0</v>
+        <v>101328.0</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="53" ht="18.75" customHeight="1">
@@ -1500,17 +1487,17 @@
         <v>66</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="D53" s="1">
         <v>1.0</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="2">
-        <v>131008.0</v>
+        <v>130581.0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" ht="18.75" customHeight="1">
@@ -1520,14 +1507,18 @@
       <c r="B54" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C54" s="4"/>
-      <c r="D54" s="2"/>
+      <c r="C54" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D54" s="1">
+        <v>1.0</v>
+      </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2">
-        <v>132844.0</v>
+        <v>131008.0</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55" ht="18.75" customHeight="1">
